--- a/data/trans_camb/P1435_2011_2023-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1435_2011_2023-Habitat-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,1</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>3,17</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,24</t>
+          <t>0,37; 2,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,47</t>
+          <t>2,84; 7,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,55</t>
+          <t>1,85; 4,37</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>387,28%</t>
+          <t>382,34%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>164,03%</t>
+          <t>160,39%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>190,72%</t>
+          <t>186,67%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,46; —</t>
+          <t>-13,88; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60,09; 334,88</t>
+          <t>61,21; 358,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,74; 379,52</t>
+          <t>74,85; 359,52</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>3,09</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,07</t>
+          <t>0,8; 2,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,63</t>
+          <t>2,74; 6,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,76</t>
+          <t>1,94; 4,14</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1196,86%</t>
+          <t>1478,23%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>108,58%</t>
+          <t>108,92%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114,4%</t>
+          <t>141,86%</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,84; 205,8</t>
+          <t>50,7; 211,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,87; 214,91</t>
+          <t>67,59; 239,36</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24,62</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,4</t>
+          <t>2,85</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,37</t>
+          <t>-0,42; 1,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 58,13</t>
+          <t>3,11; 7,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 42,99</t>
+          <t>1,63; 4,16</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>695,38%</t>
+          <t>149,51%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>701,09%</t>
+          <t>138,65%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-63,32; 775,04</t>
+          <t>-57,43; 726,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,59; 2362,75</t>
+          <t>64,47; 308,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87,91; 2712,21</t>
+          <t>59,1; 280,03</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,27</t>
+          <t>2,12</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,42</t>
+          <t>6,48</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>4,44</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,99</t>
+          <t>1,07; 3,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 8,79</t>
+          <t>4,76; 8,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,94</t>
+          <t>3,39; 5,67</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>557,03%</t>
+          <t>521,3%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>199,2%</t>
+          <t>201,04%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>241,26%</t>
+          <t>235,33%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>112,43; 2573,07</t>
+          <t>120,43; 2734,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>103,3; 362,49</t>
+          <t>111,73; 354,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>148,21; 443,29</t>
+          <t>140,76; 393,21</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10,32</t>
+          <t>5,39</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,96</t>
+          <t>3,45</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,9</t>
+          <t>0,91; 1,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,86; 24,8</t>
+          <t>4,37; 6,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,0; 17,11</t>
+          <t>2,85; 3,98</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>409,18%</t>
+          <t>425,09%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>289,8%</t>
+          <t>151,26%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>302,16%</t>
+          <t>174,73%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>163,09; 989,44</t>
+          <t>182,39; 1032,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>129,51; 814,61</t>
+          <t>109,87; 209,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>146,87; 943,83</t>
+          <t>126,28; 232,74</t>
         </is>
       </c>
     </row>
